--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2765"/>
+  <dimension ref="A1:E2766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75083,6 +75083,33 @@
         </is>
       </c>
     </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D2766" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E2766" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2766"/>
+  <dimension ref="A1:E2767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75110,6 +75110,33 @@
         </is>
       </c>
     </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2767" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2767" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
